--- a/data/fertigation/input/current-design-calculation.xlsx
+++ b/data/fertigation/input/current-design-calculation.xlsx
@@ -14,6 +14,7 @@
     <sheet sheetId="8" name="07_冲洗与均匀度" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="08_结果摘要" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="_meta" state="veryHidden" r:id="rId13"/>
+    <sheet sheetId="11" name="09_喷灌与模式" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="记录信息">'02_工况输入'!$C$5</definedName>
@@ -99,15 +100,53 @@
     <definedName name="sampleVolumeMl14">'02_工况输入'!$C$85</definedName>
     <definedName name="sampleVolumeMl15">'02_工况输入'!$C$86</definedName>
     <definedName name="sampleVolumeMl16">'02_工况输入'!$C$87</definedName>
+    <definedName name="运行模式与喷灌">'02_工况输入'!$C$88</definedName>
+    <definedName name="operatingMode">'02_工况输入'!$C$89</definedName>
+    <definedName name="sprayNozzleCount">'02_工况输入'!$C$90</definedName>
+    <definedName name="sprayNozzleFlowLph">'02_工况输入'!$C$91</definedName>
+    <definedName name="sprayPipeInnerDiameterMm">'02_工况输入'!$C$92</definedName>
+    <definedName name="sprayPipeOuterDiameterMm">'02_工况输入'!$C$93</definedName>
+    <definedName name="sprayPipeLengthM">'02_工况输入'!$C$94</definedName>
+    <definedName name="sprayPipeRoughnessMm">'02_工况输入'!$C$95</definedName>
+    <definedName name="sprayPipeLocalK">'02_工况输入'!$C$96</definedName>
+    <definedName name="sprayHeightDifferenceM">'02_工况输入'!$C$97</definedName>
+    <definedName name="fieldP4Mpa">'02_工况输入'!$C$98</definedName>
+    <definedName name="fieldP5Mpa">'02_工况输入'!$C$99</definedName>
+    <definedName name="sprayNozzleMinPressureMpa">'02_工况输入'!$C$100</definedName>
+    <definedName name="sprayNozzleMaxPressureMpa">'02_工况输入'!$C$101</definedName>
+    <definedName name="sprayDownstreamLossMpa">'02_工况输入'!$C$102</definedName>
+    <definedName name="dripValveLossMpa">'02_工况输入'!$C$103</definedName>
+    <definedName name="sprayValveLossMpa">'02_工况输入'!$C$104</definedName>
+    <definedName name="sprayFilterLossMpa">'02_工况输入'!$C$105</definedName>
+    <definedName name="sprayRegulatorSetMpa">'02_工况输入'!$C$106</definedName>
+    <definedName name="sprayRegulatorMinDifferentialMpa">'02_工况输入'!$C$107</definedName>
+    <definedName name="sprayFittingsLossMpa">'02_工况输入'!$C$108</definedName>
+    <definedName name="喷药液与喷灌文丘里工况">'02_工况输入'!$C$109</definedName>
+    <definedName name="sprayFieldP1Mpa">'02_工况输入'!$C$110</definedName>
+    <definedName name="sprayFieldP2Mpa">'02_工况输入'!$C$111</definedName>
+    <definedName name="pesticideWaterConcentration">'02_工况输入'!$C$112</definedName>
+    <definedName name="pesticideMotherConcentration">'02_工况输入'!$C$113</definedName>
+    <definedName name="pesticideTargetConcentration">'02_工况输入'!$C$114</definedName>
+    <definedName name="pesticideDurationMinutes">'02_工况输入'!$C$115</definedName>
+    <definedName name="pesticideUnusableResidualL">'02_工况输入'!$C$116</definedName>
+    <definedName name="measuredPesticideSuctionLph">'02_工况输入'!$C$117</definedName>
+    <definedName name="pesticideLabelReference">'02_工况输入'!$C$118</definedName>
+    <definedName name="pesticideMethodConfirmed">'02_工况输入'!$C$119</definedName>
+    <definedName name="sprayVenturiCurveP1Mpa">'02_工况输入'!$C$120</definedName>
+    <definedName name="sprayVenturiCurveP2Mpa">'02_工况输入'!$C$121</definedName>
+    <definedName name="sprayVenturiCurveMotiveLph">'02_工况输入'!$C$122</definedName>
+    <definedName name="sprayVenturiCurveSuctionLph">'02_工况输入'!$C$123</definedName>
+    <definedName name="sprayVenturiCurveConfirmed">'02_工况输入'!$C$124</definedName>
+    <definedName name="actualSprayFlushFlowLph">'02_工况输入'!$C$125</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="392">
-  <si>
-    <t>双路水肥系统 · 独立工程计算工作簿</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="541">
+  <si>
+    <t>双液源双末端系统 · 独立工程计算工作簿</t>
   </si>
   <si>
     <t>Excel 2016兼容 · 无宏 · 无外部链接 · 黄色为现场输入 · 蓝色为设计同步值 · 灰色为公式</t>
@@ -125,7 +164,7 @@
     <t>工作簿版本</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>生成器据此判断是否可安全同步</t>
@@ -134,7 +173,7 @@
     <t>设计版本</t>
   </si>
   <si>
-    <t>2026-07-24-v3</t>
+    <t>2026-07-24-v4</t>
   </si>
   <si>
     <t>同步后自动更新</t>
@@ -143,7 +182,7 @@
     <t>计算模型</t>
   </si>
   <si>
-    <t>单灌区、主管＋N条代表性支管</t>
+    <t>滴灌施肥＋上空喷药；两种末端分别计算</t>
   </si>
   <si>
     <t>不求解任意分支网络</t>
@@ -170,186 +209,207 @@
     <t>工况</t>
   </si>
   <si>
+    <t>V4双液源双末端边界工况</t>
+  </si>
+  <si>
+    <t>仅用于警示文丘里最低流量风险</t>
+  </si>
+  <si>
+    <t>使用顺序</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>先在“02_工况输入”填写黄色单元格。</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>A路、B路分别记录运行时动态压力；P1和P2只在B路稳定运行时读取。</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>文丘里须分别核对滴灌施肥与上空喷药的P1/P2、驱动流量和厂家曲线。</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>滴灌冲洗按末端水质恢复；喷药清水置换按喷灌管内容积并计入标签允许载水量。</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>“08_结果摘要”和“09_喷灌与模式”用于打印归档；空输入不会被自动编造。</t>
+  </si>
+  <si>
+    <t>当前设计基准（自动同步）</t>
+  </si>
+  <si>
+    <t>蓝色区域来自接口规格事实层。不要在本页修改候选接口或管径；请回到 system-interfaces.xlsx。</t>
+  </si>
+  <si>
+    <t>设计项</t>
+  </si>
+  <si>
+    <t>状态/说明</t>
+  </si>
+  <si>
+    <t>来自接口规格工作簿</t>
+  </si>
+  <si>
+    <t>核对日期</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>事实层核对日期</t>
+  </si>
+  <si>
+    <t>权威拓扑</t>
+  </si>
+  <si>
+    <t>水源→倒流防止器→过滤器→A/B互斥→合流→MV-END三通选择滴灌/喷灌</t>
+  </si>
+  <si>
+    <t>B路完整串联共用文丘里；MV-SOURCE三通选择肥料/农药</t>
+  </si>
+  <si>
+    <t>主水路候选接口</t>
+  </si>
+  <si>
+    <t>G1/2（俗称4分）</t>
+  </si>
+  <si>
+    <t>内牙/外牙及密封待厂家确认</t>
+  </si>
+  <si>
+    <t>测压口候选接口</t>
+  </si>
+  <si>
+    <t>G1/4（俗称2分）</t>
+  </si>
+  <si>
+    <t>P0–P5端口形式待厂家确认</t>
+  </si>
+  <si>
+    <t>过滤等级</t>
+  </si>
+  <si>
+    <t>120目</t>
+  </si>
+  <si>
+    <t>厂家标称微米待确认</t>
+  </si>
+  <si>
+    <t>主管</t>
+  </si>
+  <si>
+    <t>9/12 mm</t>
+  </si>
+  <si>
+    <t>内径/外径</t>
+  </si>
+  <si>
+    <t>支管</t>
+  </si>
+  <si>
+    <t>3/5 mm</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>过滤器后、控制器前</t>
+  </si>
+  <si>
+    <t>共用上游动态压力</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>文丘里入口前</t>
+  </si>
+  <si>
+    <t>B路入口压力</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>文丘里出口后、B止回阀前</t>
+  </si>
+  <si>
+    <t>与P1计算文丘里压差</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>A/B合流后、MV-END入口前</t>
+  </si>
+  <si>
+    <t>验证公共段及末端三通选择阀入口压力</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>滴灌减压阀后、滴灌主管前</t>
+  </si>
+  <si>
+    <t>验证滴头可用压力</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>最不利上空喷头入口</t>
+  </si>
+  <si>
+    <t>验证喷头工作压力</t>
+  </si>
+  <si>
+    <t>工况输入</t>
+  </si>
+  <si>
+    <t>只修改黄色C列。空值表示待确认；不要用静态压力代替运行时动态压力。A列为稳定机器字段。</t>
+  </si>
+  <si>
+    <t>机器字段</t>
+  </si>
+  <si>
+    <t>输入项</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>记录信息</t>
+  </si>
+  <si>
+    <t>scenarioName</t>
+  </si>
+  <si>
+    <t>工况名称</t>
+  </si>
+  <si>
     <t>4滴头低流量边界</t>
   </si>
   <si>
-    <t>仅用于警示文丘里最低流量风险</t>
-  </si>
-  <si>
-    <t>使用顺序</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>先在“02_工况输入”填写黄色单元格。</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>A路、B路分别记录运行时动态压力；P1和P2只在B路稳定运行时读取。</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>文丘里只有在Q驱动、P1、P2和厂家同一工况曲线均满足时才可判为适用。</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>冲洗时间由管内容积和实测流量计算，最终停止仍以末端电导率或水质恢复为准。</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>“08_结果摘要”用于打印归档；黄色输入为空不会被自动编造。</t>
-  </si>
-  <si>
-    <t>当前设计基准（自动同步）</t>
-  </si>
-  <si>
-    <t>蓝色区域来自接口规格事实层。不要在本页修改候选接口或管径；请回到 system-interfaces.xlsx。</t>
-  </si>
-  <si>
-    <t>设计项</t>
-  </si>
-  <si>
-    <t>状态/说明</t>
-  </si>
-  <si>
-    <t>来自接口规格工作簿</t>
-  </si>
-  <si>
-    <t>核对日期</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>事实层核对日期</t>
-  </si>
-  <si>
-    <t>权威拓扑</t>
-  </si>
-  <si>
-    <t>水源→倒流防止器→过滤器→双路控制器→A/B止回后合流→减压→主管</t>
-  </si>
-  <si>
-    <t>B路完整串联文丘里</t>
-  </si>
-  <si>
-    <t>主水路候选接口</t>
-  </si>
-  <si>
-    <t>G1/2（俗称4分）</t>
-  </si>
-  <si>
-    <t>内牙/外牙及密封待厂家确认</t>
-  </si>
-  <si>
-    <t>测压口候选接口</t>
-  </si>
-  <si>
-    <t>G1/4（俗称2分）</t>
-  </si>
-  <si>
-    <t>P0–P3端口形式待厂家确认</t>
-  </si>
-  <si>
-    <t>过滤等级</t>
-  </si>
-  <si>
-    <t>120目</t>
-  </si>
-  <si>
-    <t>厂家标称微米待确认</t>
-  </si>
-  <si>
-    <t>主管</t>
-  </si>
-  <si>
-    <t>9/12 mm</t>
-  </si>
-  <si>
-    <t>内径/外径</t>
-  </si>
-  <si>
-    <t>支管</t>
-  </si>
-  <si>
-    <t>3/5 mm</t>
-  </si>
-  <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>过滤器后、控制器前</t>
-  </si>
-  <si>
-    <t>共用上游动态压力</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>文丘里入口前</t>
-  </si>
-  <si>
-    <t>B路入口压力</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>文丘里出口后、B止回阀前</t>
-  </si>
-  <si>
-    <t>与P1计算文丘里压差</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>减压阀后、主管前</t>
-  </si>
-  <si>
-    <t>验证滴头可用压力</t>
-  </si>
-  <si>
-    <t>工况输入</t>
-  </si>
-  <si>
-    <t>只修改黄色C列。空值表示待确认；不要用静态压力代替运行时动态压力。A列为稳定机器字段。</t>
-  </si>
-  <si>
-    <t>机器字段</t>
-  </si>
-  <si>
-    <t>输入项</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>填写说明</t>
-  </si>
-  <si>
-    <t>记录信息</t>
-  </si>
-  <si>
-    <t>scenarioName</t>
-  </si>
-  <si>
-    <t>工况名称</t>
-  </si>
-  <si>
     <t>边界算例</t>
   </si>
   <si>
@@ -560,13 +620,16 @@
     <t>fieldP3Mpa</t>
   </si>
   <si>
-    <t>P3 减压阀后</t>
+    <t>P3 合流后、末端分配前</t>
+  </si>
+  <si>
+    <t>滴灌/喷灌均记录</t>
   </si>
   <si>
     <t>heightDifferenceM</t>
   </si>
   <si>
-    <t>滴头相对P3高差 Δz</t>
+    <t>滴头相对P4高差 Δz</t>
   </si>
   <si>
     <t>向上为正，向下为负</t>
@@ -932,6 +995,273 @@
     <t>滴头采样16</t>
   </si>
   <si>
+    <t>运行模式与喷灌</t>
+  </si>
+  <si>
+    <t>operatingMode</t>
+  </si>
+  <si>
+    <t>现场模式</t>
+  </si>
+  <si>
+    <t>滴灌施肥</t>
+  </si>
+  <si>
+    <t>停止/清水滴灌/滴灌施肥/清水喷灌/上空喷药</t>
+  </si>
+  <si>
+    <t>sprayNozzleCount</t>
+  </si>
+  <si>
+    <t>同时工作上空喷头数量 M</t>
+  </si>
+  <si>
+    <t>sprayNozzleFlowLph</t>
+  </si>
+  <si>
+    <t>单喷头标称流量</t>
+  </si>
+  <si>
+    <t>sprayPipeInnerDiameterMm</t>
+  </si>
+  <si>
+    <t>喷灌主管实际内径</t>
+  </si>
+  <si>
+    <t>sprayPipeOuterDiameterMm</t>
+  </si>
+  <si>
+    <t>喷灌主管外径</t>
+  </si>
+  <si>
+    <t>sprayPipeLengthM</t>
+  </si>
+  <si>
+    <t>喷灌主管及立管总长度</t>
+  </si>
+  <si>
+    <t>sprayPipeRoughnessMm</t>
+  </si>
+  <si>
+    <t>喷灌管绝对粗糙度 ε</t>
+  </si>
+  <si>
+    <t>sprayPipeLocalK</t>
+  </si>
+  <si>
+    <t>喷灌管局部阻力系数 ΣK</t>
+  </si>
+  <si>
+    <t>sprayHeightDifferenceM</t>
+  </si>
+  <si>
+    <t>最不利喷头相对P3高差 Δz</t>
+  </si>
+  <si>
+    <t>向上为正</t>
+  </si>
+  <si>
+    <t>fieldP4Mpa</t>
+  </si>
+  <si>
+    <t>P4 滴灌减压阀后</t>
+  </si>
+  <si>
+    <t>滴灌工况</t>
+  </si>
+  <si>
+    <t>fieldP5Mpa</t>
+  </si>
+  <si>
+    <t>P5 最不利上空喷头入口</t>
+  </si>
+  <si>
+    <t>喷灌工况</t>
+  </si>
+  <si>
+    <t>sprayNozzleMinPressureMpa</t>
+  </si>
+  <si>
+    <t>喷头最低工作压力</t>
+  </si>
+  <si>
+    <t>sprayNozzleMaxPressureMpa</t>
+  </si>
+  <si>
+    <t>喷头最高工作压力</t>
+  </si>
+  <si>
+    <t>sprayDownstreamLossMpa</t>
+  </si>
+  <si>
+    <t>喷头前其他下游压损</t>
+  </si>
+  <si>
+    <t>dripValveLossMpa</t>
+  </si>
+  <si>
+    <t>MV-END（滴灌位）当前流量压损</t>
+  </si>
+  <si>
+    <t>同一三通选择阀在滴灌设计流量下的压损</t>
+  </si>
+  <si>
+    <t>sprayValveLossMpa</t>
+  </si>
+  <si>
+    <t>MV-END（喷灌位）当前流量压损</t>
+  </si>
+  <si>
+    <t>同一三通选择阀在喷灌设计流量下的压损</t>
+  </si>
+  <si>
+    <t>sprayFilterLossMpa</t>
+  </si>
+  <si>
+    <t>喷灌支路过滤器压损</t>
+  </si>
+  <si>
+    <t>sprayRegulatorSetMpa</t>
+  </si>
+  <si>
+    <t>喷灌调压阀设定压力</t>
+  </si>
+  <si>
+    <t>sprayRegulatorMinDifferentialMpa</t>
+  </si>
+  <si>
+    <t>喷灌调压阀最小工作压差</t>
+  </si>
+  <si>
+    <t>sprayFittingsLossMpa</t>
+  </si>
+  <si>
+    <t>喷灌支路其他管件压损</t>
+  </si>
+  <si>
+    <t>喷药液与喷灌文丘里工况</t>
+  </si>
+  <si>
+    <t>sprayFieldP1Mpa</t>
+  </si>
+  <si>
+    <t>喷灌喷药工况P1</t>
+  </si>
+  <si>
+    <t>B路稳定后</t>
+  </si>
+  <si>
+    <t>sprayFieldP2Mpa</t>
+  </si>
+  <si>
+    <t>喷灌喷药工况P2</t>
+  </si>
+  <si>
+    <t>pesticideWaterConcentration</t>
+  </si>
+  <si>
+    <t>载水背景浓度</t>
+  </si>
+  <si>
+    <t>pesticideMotherConcentration</t>
+  </si>
+  <si>
+    <t>农药桶母液浓度</t>
+  </si>
+  <si>
+    <t>按标签配制</t>
+  </si>
+  <si>
+    <t>pesticideTargetConcentration</t>
+  </si>
+  <si>
+    <t>目标喷液浓度</t>
+  </si>
+  <si>
+    <t>按标签确定</t>
+  </si>
+  <si>
+    <t>pesticideDurationMinutes</t>
+  </si>
+  <si>
+    <t>B路喷药时间</t>
+  </si>
+  <si>
+    <t>计入标签允许载水量</t>
+  </si>
+  <si>
+    <t>pesticideUnusableResidualL</t>
+  </si>
+  <si>
+    <t>农药桶不可吸残余量</t>
+  </si>
+  <si>
+    <t>measuredPesticideSuctionLph</t>
+  </si>
+  <si>
+    <t>实测农药吸液流量</t>
+  </si>
+  <si>
+    <t>先用清水测试</t>
+  </si>
+  <si>
+    <t>pesticideLabelReference</t>
+  </si>
+  <si>
+    <t>农药登记标签/说明书</t>
+  </si>
+  <si>
+    <t>使用前必填</t>
+  </si>
+  <si>
+    <t>记录产品与标签版本</t>
+  </si>
+  <si>
+    <t>pesticideMethodConfirmed</t>
+  </si>
+  <si>
+    <t>标签允许所选喷施方法</t>
+  </si>
+  <si>
+    <t>未确认时禁止判定可用</t>
+  </si>
+  <si>
+    <t>sprayVenturiCurveP1Mpa</t>
+  </si>
+  <si>
+    <t>喷灌曲线工况P1</t>
+  </si>
+  <si>
+    <t>sprayVenturiCurveP2Mpa</t>
+  </si>
+  <si>
+    <t>喷灌曲线工况P2</t>
+  </si>
+  <si>
+    <t>sprayVenturiCurveMotiveLph</t>
+  </si>
+  <si>
+    <t>喷灌曲线驱动流量</t>
+  </si>
+  <si>
+    <t>sprayVenturiCurveSuctionLph</t>
+  </si>
+  <si>
+    <t>喷灌曲线吸液量</t>
+  </si>
+  <si>
+    <t>sprayVenturiCurveConfirmed</t>
+  </si>
+  <si>
+    <t>已核对喷灌厂家工况</t>
+  </si>
+  <si>
+    <t>actualSprayFlushFlowLph</t>
+  </si>
+  <si>
+    <t>实测喷灌清水置换流量</t>
+  </si>
+  <si>
     <t>管路水力</t>
   </si>
   <si>
@@ -1277,10 +1607,166 @@
     <t>先用清水完成动态压力、反向窜流、总流量、吸液量和均匀度测试。</t>
   </si>
   <si>
-    <t>fertigation-baseline:v1</t>
-  </si>
-  <si>
-    <t>2ea3d8ee0caa9532f5befac4e7a5b6f1e5ecce705506ec21d202af4f61d1ddcb</t>
+    <t>fertigation-baseline:v2</t>
+  </si>
+  <si>
+    <t>0f610613218efbc2d9c124b06da39768a04dda13bb07fbb9ffbcade3589ced82</t>
+  </si>
+  <si>
+    <t>喷灌、喷药与模式校核</t>
+  </si>
+  <si>
+    <t>只计算水力、载水量和管内容积；农药剂量及施用方法必须来自登记标签。</t>
+  </si>
+  <si>
+    <t>公式/判定</t>
+  </si>
+  <si>
+    <t>两只三通手动选择阀</t>
+  </si>
+  <si>
+    <t>按阀位卡核对 MV-END、MV-SOURCE 与 A/B 程序</t>
+  </si>
+  <si>
+    <t>模式合同</t>
+  </si>
+  <si>
+    <t>每只三通阀仅允许一个锁定位置</t>
+  </si>
+  <si>
+    <t>禁止使用无中位全关或会内部串通的三通阀</t>
+  </si>
+  <si>
+    <t>滴灌设计流量</t>
+  </si>
+  <si>
+    <t>核对滴头数量</t>
+  </si>
+  <si>
+    <t>喷灌设计流量</t>
+  </si>
+  <si>
+    <t>M×q喷头</t>
+  </si>
+  <si>
+    <t>核对喷头数量与覆盖</t>
+  </si>
+  <si>
+    <t>喷灌管内容积</t>
+  </si>
+  <si>
+    <t>πD²L/4</t>
+  </si>
+  <si>
+    <t>用于清水置换</t>
+  </si>
+  <si>
+    <t>喷灌流速</t>
+  </si>
+  <si>
+    <t>Q/A</t>
+  </si>
+  <si>
+    <t>核对管径</t>
+  </si>
+  <si>
+    <t>喷灌雷诺数</t>
+  </si>
+  <si>
+    <t>vD/ν</t>
+  </si>
+  <si>
+    <t>喷灌流态</t>
+  </si>
+  <si>
+    <t>层流/过渡区/湍流</t>
+  </si>
+  <si>
+    <t>喷灌摩阻系数</t>
+  </si>
+  <si>
+    <t>64/Re或Swamee–Jain</t>
+  </si>
+  <si>
+    <t>喷灌沿程压损</t>
+  </si>
+  <si>
+    <t>f(L/D)ρv²/2</t>
+  </si>
+  <si>
+    <t>喷灌局部压损</t>
+  </si>
+  <si>
+    <t>ΣKρv²/2</t>
+  </si>
+  <si>
+    <t>喷灌管总压损</t>
+  </si>
+  <si>
+    <t>沿程＋局部</t>
+  </si>
+  <si>
+    <t>P5喷头入口压力</t>
+  </si>
+  <si>
+    <t>现场动态压力</t>
+  </si>
+  <si>
+    <t>核对喷头范围</t>
+  </si>
+  <si>
+    <t>喷头压力判定</t>
+  </si>
+  <si>
+    <t>Pmin≤P5≤Pmax</t>
+  </si>
+  <si>
+    <t>目标农药吸液量</t>
+  </si>
+  <si>
+    <t>由用户录入的浓度平衡</t>
+  </si>
+  <si>
+    <t>不自动推荐剂量</t>
+  </si>
+  <si>
+    <t>喷药文丘里驱动流量</t>
+  </si>
+  <si>
+    <t>Q喷灌-q吸</t>
+  </si>
+  <si>
+    <t>喷灌P1-P2</t>
+  </si>
+  <si>
+    <t>喷药工况动态压差</t>
+  </si>
+  <si>
+    <t>喷药文丘里适用性</t>
+  </si>
+  <si>
+    <t>标签＋厂家工况＋现场水力</t>
+  </si>
+  <si>
+    <t>缺任一项保持待确认</t>
+  </si>
+  <si>
+    <t>喷灌理论置换时间</t>
+  </si>
+  <si>
+    <t>V喷灌/Q清水×60</t>
+  </si>
+  <si>
+    <t>不计算农药推荐剂量</t>
+  </si>
+  <si>
+    <t>固定</t>
+  </si>
+  <si>
+    <t>只提供工程水力</t>
+  </si>
+  <si>
+    <t>按登记标签执行</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1778,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1329,6 +1815,11 @@
       <name val="Microsoft YaHei"/>
     </font>
     <font>
+      <color theme="1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFEDF4F8"/>
       <sz val="6"/>
@@ -1347,6 +1838,22 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF526B80"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF8293A3"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1F3346"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Microsoft YaHei"/>
@@ -1357,8 +1864,31 @@
       <sz val="9"/>
       <name val="Microsoft YaHei"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF60768A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1397,6 +1927,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEDF1F5"/>
       </patternFill>
     </fill>
@@ -1410,8 +1945,23 @@
         <fgColor rgb="FFC84343"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF173A5B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1769AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1454,11 +2004,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8E3EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8E3EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8E3EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1476,37 +2046,37 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1522,34 +2092,96 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1561,7 +2193,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -1572,7 +2204,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -1583,7 +2215,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -1594,7 +2226,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -1605,7 +2237,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -1616,7 +2248,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -1627,7 +2259,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -1638,7 +2270,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -1649,7 +2281,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -1660,7 +2292,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -1671,7 +2303,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -1682,7 +2314,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -1693,7 +2325,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -1704,7 +2336,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -1715,7 +2347,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -1726,7 +2358,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -2148,16 +2780,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>390</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>391</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -2168,13 +2800,470 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.600000381469727" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="44" t="str">
+        <f>'02_工况输入'!$C$89</f>
+        <v>滴灌施肥</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45" t="str">
+        <f>IF(B5="","待确认",IF(OR(B5="不适用",B5="待厂家确认",B5="待确认"),B5,"已计算"))</f>
+        <v>已计算</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="B6" s="47" t="str">
+        <f>IF(OR(B5="停止",B5="清水滴灌",B5="滴灌施肥",B5="清水喷灌",B5="上空喷药"),"允许","不适用")</f>
+        <v>允许</v>
+      </c>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48" t="str">
+        <f>IF(B6="允许","已计算","不适用")</f>
+        <v>已计算</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>495</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="B7" s="47">
+        <f>'03_管路水力'!B5</f>
+        <v>8</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="48" t="str">
+        <f>IF(B7="","待确认",IF(OR(B7="不适用",B7="待厂家确认",B7="待确认"),B7,"已计算"))</f>
+        <v>已计算</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="49">
+        <f>IF(OR('02_工况输入'!$C$90="",'02_工况输入'!$C$91=""),"",'02_工况输入'!$C$90*'02_工况输入'!$C$91)</f>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="48" t="str">
+        <f>IF(B8="","待确认",IF(OR(B8="不适用",B8="待厂家确认",B8="待确认"),B8,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>500</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" s="49">
+        <f>IF(OR('02_工况输入'!$C$92="",'02_工况输入'!$C$94=""),"",PI()*('02_工况输入'!$C$92/1000)^2/4*'02_工况输入'!$C$94*1000)</f>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="48" t="str">
+        <f>IF(B9="","待确认",IF(OR(B9="不适用",B9="待厂家确认",B9="待确认"),B9,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>503</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="B10" s="49">
+        <f>IF(OR(B8="",'02_工况输入'!$C$92=""),"",B8/3600000/(PI()*('02_工况输入'!$C$92/1000)^2/4))</f>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="48" t="str">
+        <f>IF(B10="","待确认",IF(OR(B10="不适用",B10="待厂家确认",B10="待确认"),B10,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>506</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="46" t="s">
+        <v>508</v>
+      </c>
+      <c r="B11" s="49">
+        <f>IF(OR(B10="",'02_工况输入'!$C$92="",'02_工况输入'!$C$13=""),"",B10*('02_工况输入'!$C$92/1000)/'02_工况输入'!$C$13)</f>
+      </c>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48" t="str">
+        <f>IF(B11="","待确认",IF(OR(B11="不适用",B11="待厂家确认",B11="待确认"),B11,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="F11" s="48"/>
+    </row>
+    <row r="12" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="B12" s="49" t="str">
+        <f>IF(B11="","待确认",IF(B11&lt;2300,"层流",IF(B11&lt;4000,"过渡区","湍流")))</f>
+        <v>待确认</v>
+      </c>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48" t="s">
+        <v>511</v>
+      </c>
+      <c r="F12" s="48"/>
+    </row>
+    <row r="13" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="B13" s="49">
+        <f>IF(B11="","",IF(B11&lt;2300,64/B11,IF(OR(B11&lt;4000,'02_工况输入'!$C$95=""),"",0.25/(LOG10(('02_工况输入'!$C$95/1000)/(3.7*('02_工况输入'!$C$92/1000))+5.74/(B11^0.9))^2))))</f>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48" t="str">
+        <f>IF(B13="","待确认",IF(OR(B13="不适用",B13="待厂家确认",B13="待确认"),B13,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>513</v>
+      </c>
+      <c r="F13" s="48"/>
+    </row>
+    <row r="14" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>514</v>
+      </c>
+      <c r="B14" s="49">
+        <f>IF(OR(B13="",B10="",'02_工况输入'!$C$94="",'02_工况输入'!$C$92=""),"",B13*('02_工况输入'!$C$94/('02_工况输入'!$C$92/1000))*('02_工况输入'!$C$12*B10^2/2)/1000000)</f>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="48" t="str">
+        <f>IF(B14="","待确认",IF(OR(B14="不适用",B14="待厂家确认",B14="待确认"),B14,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>515</v>
+      </c>
+      <c r="F14" s="48"/>
+    </row>
+    <row r="15" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" s="49">
+        <f>IF(OR(B10="",'02_工况输入'!$C$96=""),"",'02_工况输入'!$C$96*('02_工况输入'!$C$12*B10^2/2)/1000000)</f>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="48" t="str">
+        <f>IF(B15="","待确认",IF(OR(B15="不适用",B15="待厂家确认",B15="待确认"),B15,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="F15" s="48"/>
+    </row>
+    <row r="16" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>518</v>
+      </c>
+      <c r="B16" s="49">
+        <f>IF(OR(B14="",B15=""),"",B14+B15)</f>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="48" t="str">
+        <f>IF(B16="","待确认",IF(OR(B16="不适用",B16="待厂家确认",B16="待确认"),B16,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="F16" s="48"/>
+    </row>
+    <row r="17" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="B17" s="49">
+        <f>IF('02_工况输入'!$C$99=0,"",'02_工况输入'!$C$99)</f>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="48" t="str">
+        <f>IF(B17="","待确认",IF(OR(B17="不适用",B17="待厂家确认",B17="待确认"),B17,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>521</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="18" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="46" t="s">
+        <v>523</v>
+      </c>
+      <c r="B18" s="47" t="str">
+        <f>IF(OR(B17="",'02_工况输入'!$C$100="",'02_工况输入'!$C$101=""),"待确认",IF(AND(B17&gt;='02_工况输入'!$C$100,B17&lt;='02_工况输入'!$C$101),"已计算","不适用"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48" t="str">
+        <f>B18</f>
+        <v>待确认</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>524</v>
+      </c>
+      <c r="F18" s="48"/>
+    </row>
+    <row r="19" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
+        <v>525</v>
+      </c>
+      <c r="B19" s="49">
+        <f>IF(OR(B8="",'02_工况输入'!$C$113="",'02_工况输入'!$C$114=""),"",IF(OR('02_工况输入'!$C$113&lt;='02_工况输入'!$C$112,'02_工况输入'!$C$114&lt;='02_工况输入'!$C$112,'02_工况输入'!$C$114&gt;='02_工况输入'!$C$113),"",B8*('02_工况输入'!$C$114-'02_工况输入'!$C$112)/('02_工况输入'!$C$113-'02_工况输入'!$C$112)))</f>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="48" t="str">
+        <f>IF(B19="","待确认",IF(OR(B19="不适用",B19="待厂家确认",B19="待确认"),B19,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E19" s="48" t="s">
+        <v>526</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="20" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
+        <v>528</v>
+      </c>
+      <c r="B20" s="49">
+        <f>IF(OR(B8="",B19=""),"",B8-B19)</f>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="48" t="str">
+        <f>IF(B20="","待确认",IF(OR(B20="不适用",B20="待厂家确认",B20="待确认"),B20,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>529</v>
+      </c>
+      <c r="F20" s="48"/>
+    </row>
+    <row r="21" ht="26.399999618530273" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
+        <v>530</v>
+      </c>
+      <c r="B21" s="49">
+        <f>IF(OR('02_工况输入'!$C$110="",'02_工况输入'!$C$111=""),"",'02_工况输入'!$C$110-'02_工况输入'!$C$111)</f>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="48" t="str">
+        <f>IF(B21="","待确认",IF(OR(B21="不适用",B21="待厂家确认",B21="待确认"),B21,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>531</v>
+      </c>
+      <c r="F21" s="48"/>
+    </row>
+    <row r="22" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>532</v>
+      </c>
+      <c r="B22" s="49" t="str">
+        <f>IF('02_工况输入'!$C$119&lt;&gt;TRUE,"待确认",IF('02_工况输入'!$C$124&lt;&gt;TRUE,"待厂家确认",IF(OR(B20="",B21="",'02_工况输入'!$C$120="",'02_工况输入'!$C$121="",'02_工况输入'!$C$122="",'02_工况输入'!$C$123=""),"待确认",IF(OR(B21&lt;=0,B19&gt;'02_工况输入'!$C$123),"不适用","已计算"))))</f>
+        <v>待确认</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48" t="str">
+        <f>B22</f>
+        <v>待确认</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>533</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>535</v>
+      </c>
+      <c r="B23" s="49">
+        <f>IF(OR(B9="",'02_工况输入'!$C$125=""),"",B9/'02_工况输入'!$C$125*60)</f>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" s="48" t="str">
+        <f>IF(B23="","待确认",IF(OR(B23="不适用",B23="待厂家确认",B23="待确认"),B23,"已计算"))</f>
+        <v>待确认</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>536</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" ht="39.599998474121094" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48" t="s">
+        <v>538</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>539</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2354,6 +3443,28 @@
       </c>
       <c r="C16" s="9" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2368,20 +3479,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2391,7 +3502,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2401,27 +3512,27 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
@@ -2431,57 +3542,57 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
@@ -2491,82 +3602,82 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C10" s="18">
         <v>4</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C11" s="19">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C12" s="19">
         <v>1000</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C13" s="19">
         <v>0.000001004</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2581,105 +3692,105 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C15" s="19">
         <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C16" s="19">
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C17" s="19">
         <v>10</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C19" s="19">
         <v>0</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -2689,105 +3800,105 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C21" s="19">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C22" s="19">
         <v>5</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C23" s="19">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C24" s="19">
         <v>0</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C25" s="19">
         <v>0</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="17"/>
@@ -2797,165 +3908,167 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C32" s="19">
         <v>0</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C33" s="19">
         <v>0</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="17"/>
@@ -2965,93 +4078,93 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C41" s="19"/>
       <c r="D41" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="17"/>
@@ -3061,57 +4174,57 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="17"/>
@@ -3121,73 +4234,73 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C47" s="19"/>
       <c r="D47" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F47" s="5"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C48" s="19"/>
       <c r="D48" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C49" s="19"/>
       <c r="D49" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F49" s="5"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F50" s="5"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="17"/>
@@ -3197,109 +4310,109 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C52" s="19">
         <v>0</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F54" s="5"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C56" s="19">
         <v>0</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F56" s="5"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C57" s="19"/>
       <c r="D57" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F57" s="5"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="17"/>
@@ -3309,167 +4422,167 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C63" s="19"/>
       <c r="D63" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F63" s="5"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C64" s="19"/>
       <c r="D64" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F64" s="5"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F65" s="5"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F66" s="5"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="17"/>
@@ -3479,325 +4592,947 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C71" s="19">
         <v>10</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C75" s="19"/>
       <c r="D75" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C77" s="19"/>
       <c r="D77" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C82" s="19"/>
       <c r="D82" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C83" s="19"/>
       <c r="D83" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C84" s="19"/>
       <c r="D84" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C85" s="19"/>
       <c r="D85" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C86" s="19"/>
       <c r="D86" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C87" s="19"/>
       <c r="D87" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>244</v>
-      </c>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B88" s="21"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="21"/>
+    </row>
+    <row r="89" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="C90" s="26"/>
+      <c r="D90" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F90" s="24"/>
+    </row>
+    <row r="91" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" s="27"/>
+      <c r="D91" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E91" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F91" s="24"/>
+    </row>
+    <row r="92" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" s="27"/>
+      <c r="D92" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E92" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F92" s="24"/>
+    </row>
+    <row r="93" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" s="27"/>
+      <c r="D93" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E93" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F93" s="24"/>
+    </row>
+    <row r="94" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="B94" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="24"/>
+    </row>
+    <row r="95" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="C95" s="27"/>
+      <c r="D95" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E95" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F95" s="24"/>
+    </row>
+    <row r="96" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96" s="27"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F96" s="24"/>
+    </row>
+    <row r="97" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C97" s="27">
+        <v>0</v>
+      </c>
+      <c r="D97" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E97" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F97" s="24" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C98" s="27"/>
+      <c r="D98" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E98" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F98" s="24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="C99" s="27"/>
+      <c r="D99" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E99" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" s="24" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="C100" s="27"/>
+      <c r="D100" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F100" s="24"/>
+    </row>
+    <row r="101" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="C101" s="27"/>
+      <c r="D101" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E101" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F101" s="24"/>
+    </row>
+    <row r="102" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="C102" s="27">
+        <v>0</v>
+      </c>
+      <c r="D102" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E102" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F102" s="24"/>
+    </row>
+    <row r="103" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="C103" s="27"/>
+      <c r="D103" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E103" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F103" s="24"/>
+    </row>
+    <row r="104" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="C104" s="27"/>
+      <c r="D104" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="E104" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F104" s="24"/>
+    </row>
+    <row r="105" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="C105" s="27"/>
+      <c r="D105" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E105" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F105" s="24"/>
+    </row>
+    <row r="106" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="C106" s="27"/>
+      <c r="D106" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F106" s="24"/>
+    </row>
+    <row r="107" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="C107" s="27"/>
+      <c r="D107" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E107" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F107" s="24"/>
+    </row>
+    <row r="108" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C108" s="27"/>
+      <c r="D108" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F108" s="24"/>
+    </row>
+    <row r="109" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="B109" s="21"/>
+      <c r="C109" s="22"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="21"/>
+    </row>
+    <row r="110" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C110" s="27"/>
+      <c r="D110" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E110" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F110" s="24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C111" s="27"/>
+      <c r="D111" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E111" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F111" s="24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="C112" s="27">
+        <v>0</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F112" s="24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="B113" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="C113" s="27"/>
+      <c r="D113" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E113" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="F113" s="24"/>
+    </row>
+    <row r="114" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="C114" s="27"/>
+      <c r="D114" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E114" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="F114" s="24"/>
+    </row>
+    <row r="115" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="C115" s="27"/>
+      <c r="D115" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="E115" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F115" s="24" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="C116" s="27">
+        <v>0</v>
+      </c>
+      <c r="D116" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E116" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F116" s="24"/>
+    </row>
+    <row r="117" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="C117" s="27"/>
+      <c r="D117" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E117" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F117" s="24" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="B118" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="C118" s="25"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="F118" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="C119" s="28"/>
+      <c r="D119" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E119" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="F119" s="24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="C120" s="27"/>
+      <c r="D120" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E120" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F120" s="24"/>
+    </row>
+    <row r="121" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="C121" s="27"/>
+      <c r="D121" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E121" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F121" s="24"/>
+    </row>
+    <row r="122" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="B122" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="C122" s="27"/>
+      <c r="D122" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E122" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F122" s="24"/>
+    </row>
+    <row r="123" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C123" s="27"/>
+      <c r="D123" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E123" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F123" s="24"/>
+    </row>
+    <row r="124" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" s="28"/>
+      <c r="D124" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F124" s="24"/>
+    </row>
+    <row r="125" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="C125" s="27"/>
+      <c r="D125" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E125" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F125" s="24"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
@@ -3830,9 +5565,18 @@
       <formula>NOT(ISERROR(SEARCH("undefined",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="C119">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C124">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="C68">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C89">
+      <formula1>"停止,清水滴灌,滴灌施肥,清水喷灌,上空喷药"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3851,7 +5595,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3859,7 +5603,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3873,259 +5617,259 @@
         <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B5" s="21">
+        <v>375</v>
+      </c>
+      <c r="B5" s="29">
         <f>'02_工况输入'!$C$10*'02_工况输入'!$C$11</f>
         <v>8</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="29">
         <f>'02_工况输入'!$C$11</f>
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="22">
+        <v>376</v>
+      </c>
+      <c r="B6" s="30">
         <f>B5/3600000</f>
         <v>0.000002222222222222222</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="30">
         <f>C5/3600000</f>
         <v>5.555555555555555e-7</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B7" s="22">
+        <v>378</v>
+      </c>
+      <c r="B7" s="30">
         <f>'02_工况输入'!$C$15</f>
         <v>9</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="30">
         <f>'02_工况输入'!$C$21</f>
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B8" s="22">
+        <v>379</v>
+      </c>
+      <c r="B8" s="30">
         <f>'02_工况输入'!$C$17</f>
         <v>10</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="30">
         <f>'02_工况输入'!$C$23</f>
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="22">
+        <v>380</v>
+      </c>
+      <c r="B9" s="30">
         <f>'02_工况输入'!$C$18</f>
         <v>0</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="30">
         <f>'02_工况输入'!$C$24</f>
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B10" s="22">
+        <v>381</v>
+      </c>
+      <c r="B10" s="30">
         <f>'02_工况输入'!$C$19</f>
         <v>0</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="30">
         <f>'02_工况输入'!$C$25</f>
         <v>0</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B11" s="22">
+        <v>383</v>
+      </c>
+      <c r="B11" s="30">
         <f>PI()*(B7/1000)^2/4</f>
         <v>0.0000636172512351933</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="30">
         <f>PI()*(C7/1000)^2/4</f>
         <v>0.000007068583470577034</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B12" s="22">
+        <v>385</v>
+      </c>
+      <c r="B12" s="30">
         <f>IF(OR(B6="",B11&lt;=0),"",B6/B11)</f>
         <v>0.03493112605583437</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="30">
         <f>IF(OR(C6="",C11&lt;=0),"",C6/C11)</f>
         <v>0.07859503362562732</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="22">
+        <v>387</v>
+      </c>
+      <c r="B13" s="30">
         <f>IF(OR(B12="",B7&lt;=0),"",B12*(B7/1000)/'02_工况输入'!$C$13)</f>
         <v>313.1276240064834</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="30">
         <f>IF(OR(C12="",C7&lt;=0),"",C12*(C7/1000)/'02_工况输入'!$C$13)</f>
         <v>234.84571800486253</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="22" t="str">
+        <v>388</v>
+      </c>
+      <c r="B14" s="30" t="str">
         <f>IF(B13="","待确认",IF(B13&lt;2300,"层流",IF(B13&lt;4000,"过渡区","湍流")))</f>
         <v>层流</v>
       </c>
-      <c r="C14" s="22" t="str">
+      <c r="C14" s="30" t="str">
         <f>IF(C13="","待确认",IF(C13&lt;2300,"层流",IF(C13&lt;4000,"过渡区","湍流")))</f>
         <v>层流</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="22">
+        <v>389</v>
+      </c>
+      <c r="B15" s="30">
         <f>IF(B13="","",IF(B13&lt;2300,64/B13,IF(OR(B13&lt;4000,B9=""),"",0.25/(LOG10((B9/1000/(B7/1000))/3.7+5.74/B13^0.9)^2))))</f>
         <v>0.20438950476842904</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="30">
         <f>IF(C13="","",IF(C13&lt;2300,64/C13,IF(OR(C13&lt;4000,C9=""),"",0.25/(LOG10((C9/1000/(C7/1000))/3.7+5.74/C13^0.9)^2))))</f>
         <v>0.27251933969123876</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="22">
+        <v>390</v>
+      </c>
+      <c r="B16" s="30">
         <f>IF(B15="","",B15*(B8/(B7/1000))*('02_工况输入'!$C$12*B12^2/2)/1000000)</f>
         <v>0.00013855150838541314</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="30">
         <f>IF(C15="","",C15*(C8/(C7/1000))*('02_工况输入'!$C$12*C12^2/2)/1000000)</f>
         <v>0.0002805668044804616</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B17" s="22">
+        <v>391</v>
+      </c>
+      <c r="B17" s="30">
         <f>IF(OR(B12="",B10=""),"",B10*('02_工况输入'!$C$12*B12^2/2)/1000000)</f>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="30">
         <f>IF(OR(C12="",C10=""),"",C10*('02_工况输入'!$C$12*C12^2/2)/1000000)</f>
       </c>
       <c r="D17" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B18" s="22">
+        <v>392</v>
+      </c>
+      <c r="B18" s="30">
         <f>IF(OR(B16="",B17=""),"",B16+B17)</f>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="30">
         <f>IF(OR(C16="",C17=""),"",C16+C17)</f>
       </c>
       <c r="D18" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="22">
+        <v>393</v>
+      </c>
+      <c r="B19" s="30">
         <f>PI()*(B7/1000)^2/4*B8*1000</f>
         <v>0.6361725123519331</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="30">
         <f>PI()*(C7/1000)^2/4*C8*1000</f>
         <v>0.007068583470577035</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B21" s="23">
+        <v>394</v>
+      </c>
+      <c r="B21" s="31">
         <f>B19+'02_工况输入'!$C$10*C19</f>
         <v>0.6644468462342412</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>298</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -4150,7 +5894,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4158,7 +5902,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4169,127 +5913,127 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>303</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="21">
+        <v>146</v>
+      </c>
+      <c r="B5" s="29">
         <f>IF('02_工况输入'!$C$27=0,"",'02_工况输入'!$C$27)</f>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="29">
         <f>IF('02_工况输入'!$C$27=0,"",'02_工况输入'!$C$27)</f>
       </c>
       <c r="D5" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="22">
+        <v>173</v>
+      </c>
+      <c r="B6" s="30">
         <f>IF('02_工况输入'!$C$37=0,"",'02_工况输入'!$C$37)</f>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="30">
         <f>IF('02_工况输入'!$C$37=0,"",'02_工况输入'!$C$37)</f>
       </c>
       <c r="D6" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="22">
+        <v>175</v>
+      </c>
+      <c r="B7" s="30">
         <f>IF('02_工况输入'!$C$38=0,"",'02_工况输入'!$C$38)</f>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="30">
         <f>IF('02_工况输入'!$C$38=0,"",'02_工况输入'!$C$38)</f>
       </c>
       <c r="D7" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B8" s="22">
+        <v>401</v>
+      </c>
+      <c r="B8" s="30">
         <f>IF(OR('02_工况输入'!$C$39="",'02_工况输入'!$C$40="",'02_工况输入'!$C$43="",'02_工况输入'!$C$44="",'02_工况输入'!$C$45=""),"",'02_工况输入'!$C$39+'02_工况输入'!$C$40+'02_工况输入'!$C$43+'02_工况输入'!$C$44+'02_工况输入'!$C$45)</f>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="30">
         <f>IF(OR('02_工况输入'!$C$39="",'02_工况输入'!$C$41="",'02_工况输入'!$C$43="",'02_工况输入'!$C$44="",'02_工况输入'!$C$45=""),"",'02_工况输入'!$C$39+'02_工况输入'!$C$41+'02_工况输入'!$C$43+'02_工况输入'!$C$44+'02_工况输入'!$C$45)</f>
       </c>
       <c r="D8" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" s="22">
+        <v>402</v>
+      </c>
+      <c r="B9" s="30">
         <f>IF(OR(B6="",B7="",B8=""),"",B6+B7+B8)</f>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="30">
         <f>IF(OR(C6="",C7="",C8=""),"",C6+C7+C8)</f>
       </c>
       <c r="D9" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B10" s="22">
+        <v>403</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(OR(B5="",B9=""),"",B5-B9)</f>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="30">
         <f>IF(OR(C5="",C9=""),"",C5-C9)</f>
       </c>
       <c r="D10" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B11" s="24" t="str">
+        <v>404</v>
+      </c>
+      <c r="B11" s="32" t="str">
         <f>IF(B10="","待确认",IF(B10&gt;=0,"已计算","不适用"))</f>
         <v>待确认</v>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="32" t="str">
         <f>IF(C10="","待确认",IF(C10&gt;=0,"已计算","不适用"))</f>
         <v>待确认</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>308</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>310</v>
+      <c r="B12" s="32" t="s">
+        <v>406</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>407</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>311</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4328,7 +6072,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4337,7 +6081,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4349,203 +6093,203 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>317</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="29">
         <f>IF('02_工况输入'!$C$29=0,"",'02_工况输入'!$C$29)</f>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="30">
         <f>IF('02_工况输入'!$C$30=0,"",'02_工况输入'!$C$30)</f>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="22">
+        <v>415</v>
+      </c>
+      <c r="B7" s="30">
         <f>IF(OR(B5="",B6=""),"",B5-B6)</f>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="5" t="s">
-        <v>319</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="22">
+        <v>417</v>
+      </c>
+      <c r="B8" s="30">
         <f>'03_管路水力'!B5</f>
         <v>8</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B9" s="22">
+        <v>418</v>
+      </c>
+      <c r="B9" s="30">
         <f>'06_肥液与桶'!B10</f>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="22">
+        <v>419</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(OR(B8="",B9=""),"",B8-B9)</f>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="5" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B11" s="22">
+        <v>421</v>
+      </c>
+      <c r="B11" s="30">
         <f>IF('02_工况输入'!$C$61=0,"",'02_工况输入'!$C$61)</f>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22">
+        <v>422</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30">
         <f>IF('02_工况输入'!$C$62=0,"",'02_工况输入'!$C$62)</f>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="30">
         <f>IF('02_工况输入'!$C$63=0,"",'02_工况输入'!$C$63)</f>
       </c>
       <c r="E12" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22">
+        <v>423</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30">
         <f>IF('02_工况输入'!$C$64=0,"",'02_工况输入'!$C$64)</f>
       </c>
       <c r="E13" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22">
+        <v>424</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30">
         <f>IF('02_工况输入'!$C$65=0,"",'02_工况输入'!$C$65)</f>
       </c>
       <c r="E14" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22">
+        <v>425</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30">
         <f>IF('02_工况输入'!$C$66=0,"",'02_工况输入'!$C$66)</f>
       </c>
       <c r="E15" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22">
+        <v>426</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30">
         <f>IF('02_工况输入'!$C$67=0,"",'02_工况输入'!$C$67)</f>
       </c>
       <c r="E16" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" s="24" t="b">
+        <v>427</v>
+      </c>
+      <c r="B17" s="32">
         <f>'02_工况输入'!$C$68</f>
         <v>0</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
       <c r="E17" s="5" t="s">
-        <v>331</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" s="24" t="str">
+        <v>429</v>
+      </c>
+      <c r="B18" s="32" t="str">
         <f>IF(B17&lt;&gt;TRUE,"待厂家确认",IF(OR(B5="",B6="",B10="",B11="",C12="",D12="",D13="",D14="",D15="",D16=""),"待确认",IF(OR(B5&gt;B11,B10&lt;C12,B10&gt;D12,B9&gt;D16),"不适用","已计算")))</f>
         <v>待厂家确认</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
       <c r="E18" s="5" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -4585,7 +6329,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4593,7 +6337,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>432</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4604,152 +6348,152 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>336</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="21">
+        <v>417</v>
+      </c>
+      <c r="B5" s="29">
         <f>'03_管路水力'!B5</f>
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B6" s="22">
+        <v>435</v>
+      </c>
+      <c r="B6" s="30">
         <f>'02_工况输入'!$C$52</f>
         <v>0</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>339</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B7" s="22">
+        <v>437</v>
+      </c>
+      <c r="B7" s="30">
         <f>IF('02_工况输入'!$C$53=0,"",'02_工况输入'!$C$53)</f>
       </c>
       <c r="C7" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>341</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="B8" s="22">
+        <v>439</v>
+      </c>
+      <c r="B8" s="30">
         <f>IF('02_工况输入'!$C$54=0,"",'02_工况输入'!$C$54)</f>
       </c>
       <c r="C8" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="B9" s="22">
+        <v>441</v>
+      </c>
+      <c r="B9" s="30">
         <f>IF('02_工况输入'!$C$55=0,"",'02_工况输入'!$C$55)</f>
       </c>
       <c r="C9" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B10" s="22">
+        <v>418</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(OR(B7="",B8=""),"",IF(OR(B7&lt;=B6,B8&lt;B6,B8&gt;=B7),"",B5*(B8-B6)/(B7-B6)))</f>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B11" s="22">
+        <v>443</v>
+      </c>
+      <c r="B11" s="30">
         <f>IF(OR(B5="",B10=""),"",B5-B10)</f>
       </c>
       <c r="C11" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="B12" s="22">
+        <v>444</v>
+      </c>
+      <c r="B12" s="30">
         <f>IF(OR(B10="",B9=""),"",B10*B9/60)</f>
       </c>
       <c r="C12" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>348</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="22">
+        <v>216</v>
+      </c>
+      <c r="B13" s="30">
         <f>'02_工况输入'!$C$56</f>
         <v>0</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B14" s="22">
+        <v>446</v>
+      </c>
+      <c r="B14" s="30">
         <f>IF(B12="","",B12+B13)</f>
       </c>
       <c r="C14" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>350</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -4775,7 +6519,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4785,7 +6529,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4795,19 +6539,19 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>450</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>357</v>
+        <v>454</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>4</v>
@@ -4817,13 +6561,13 @@
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="33">
         <f>IF('02_工况输入'!$C$72=0,"",'02_工况输入'!$C$72)</f>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="33">
         <f>IF(OR(B5="",'02_工况输入'!$C$71&lt;=0),"",B5*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="33">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E5" s="4"/>
@@ -4833,13 +6577,13 @@
       <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="34">
         <f>IF('02_工况输入'!$C$73=0,"",'02_工况输入'!$C$73)</f>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="34">
         <f>IF(OR(B6="",'02_工况输入'!$C$71&lt;=0),"",B6*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E6" s="5"/>
@@ -4849,13 +6593,13 @@
       <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="34">
         <f>IF('02_工况输入'!$C$74=0,"",'02_工况输入'!$C$74)</f>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="34">
         <f>IF(OR(B7="",'02_工况输入'!$C$71&lt;=0),"",B7*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E7" s="5"/>
@@ -4865,13 +6609,13 @@
       <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="34">
         <f>IF('02_工况输入'!$C$75=0,"",'02_工况输入'!$C$75)</f>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="34">
         <f>IF(OR(B8="",'02_工况输入'!$C$71&lt;=0),"",B8*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E8" s="5"/>
@@ -4881,13 +6625,13 @@
       <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="34">
         <f>IF('02_工况输入'!$C$76=0,"",'02_工况输入'!$C$76)</f>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="34">
         <f>IF(OR(B9="",'02_工况输入'!$C$71&lt;=0),"",B9*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E9" s="5"/>
@@ -4897,13 +6641,13 @@
       <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="34">
         <f>IF('02_工况输入'!$C$77=0,"",'02_工况输入'!$C$77)</f>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="34">
         <f>IF(OR(B10="",'02_工况输入'!$C$71&lt;=0),"",B10*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E10" s="5"/>
@@ -4913,13 +6657,13 @@
       <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="34">
         <f>IF('02_工况输入'!$C$78=0,"",'02_工况输入'!$C$78)</f>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="34">
         <f>IF(OR(B11="",'02_工况输入'!$C$71&lt;=0),"",B11*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E11" s="5"/>
@@ -4929,13 +6673,13 @@
       <c r="A12" s="5">
         <v>8</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="34">
         <f>IF('02_工况输入'!$C$79=0,"",'02_工况输入'!$C$79)</f>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="34">
         <f>IF(OR(B12="",'02_工况输入'!$C$71&lt;=0),"",B12*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E12" s="5"/>
@@ -4945,13 +6689,13 @@
       <c r="A13" s="5">
         <v>9</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="34">
         <f>IF('02_工况输入'!$C$80=0,"",'02_工况输入'!$C$80)</f>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="34">
         <f>IF(OR(B13="",'02_工况输入'!$C$71&lt;=0),"",B13*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E13" s="5"/>
@@ -4961,13 +6705,13 @@
       <c r="A14" s="5">
         <v>10</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="34">
         <f>IF('02_工况输入'!$C$81=0,"",'02_工况输入'!$C$81)</f>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="34">
         <f>IF(OR(B14="",'02_工况输入'!$C$71&lt;=0),"",B14*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E14" s="5"/>
@@ -4977,13 +6721,13 @@
       <c r="A15" s="5">
         <v>11</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="34">
         <f>IF('02_工况输入'!$C$82=0,"",'02_工况输入'!$C$82)</f>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="34">
         <f>IF(OR(B15="",'02_工况输入'!$C$71&lt;=0),"",B15*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E15" s="5"/>
@@ -4993,13 +6737,13 @@
       <c r="A16" s="5">
         <v>12</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="34">
         <f>IF('02_工况输入'!$C$83=0,"",'02_工况输入'!$C$83)</f>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="34">
         <f>IF(OR(B16="",'02_工况输入'!$C$71&lt;=0),"",B16*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E16" s="5"/>
@@ -5009,13 +6753,13 @@
       <c r="A17" s="5">
         <v>13</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="34">
         <f>IF('02_工况输入'!$C$84=0,"",'02_工况输入'!$C$84)</f>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="34">
         <f>IF(OR(B17="",'02_工况输入'!$C$71&lt;=0),"",B17*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E17" s="5"/>
@@ -5025,13 +6769,13 @@
       <c r="A18" s="5">
         <v>14</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="34">
         <f>IF('02_工况输入'!$C$85=0,"",'02_工况输入'!$C$85)</f>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="34">
         <f>IF(OR(B18="",'02_工况输入'!$C$71&lt;=0),"",B18*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E18" s="5"/>
@@ -5041,13 +6785,13 @@
       <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="34">
         <f>IF('02_工况输入'!$C$86=0,"",'02_工况输入'!$C$86)</f>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="34">
         <f>IF(OR(B19="",'02_工况输入'!$C$71&lt;=0),"",B19*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E19" s="5"/>
@@ -5057,13 +6801,13 @@
       <c r="A20" s="5">
         <v>16</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="34">
         <f>IF('02_工况输入'!$C$87=0,"",'02_工况输入'!$C$87)</f>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="34">
         <f>IF(OR(B20="",'02_工况输入'!$C$71&lt;=0),"",B20*60/(1000*'02_工况输入'!$C$71))</f>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="34">
         <f>IF(ROW()-4&lt;=COUNT('02_工况输入'!$C$72:$C$87)/4,SMALL($C$5:$C$20,ROW()-4),"")</f>
       </c>
       <c r="E20" s="5"/>
@@ -5071,7 +6815,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>358</v>
+        <v>455</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -5081,62 +6825,62 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B24" s="27">
+        <v>394</v>
+      </c>
+      <c r="B24" s="35">
         <f>'03_管路水力'!B21</f>
         <v>0.6644468462342412</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>359</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B25" s="24">
+        <v>246</v>
+      </c>
+      <c r="B25" s="32">
         <f>IF('02_工况输入'!$C$70=0,"",'02_工况输入'!$C$70)</f>
       </c>
       <c r="C25" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B26" s="24">
+        <v>458</v>
+      </c>
+      <c r="B26" s="32">
         <f>IF(OR(B24="",B25&lt;=0),"",B24/B25*60)</f>
       </c>
       <c r="C26" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>362</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="B27" s="24">
+        <v>460</v>
+      </c>
+      <c r="B27" s="32">
         <f>IF(COUNT('02_工况输入'!$C$72:$C$87)&lt;4,"",AVERAGE(C5:C20))</f>
       </c>
       <c r="C27" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -5144,20 +6888,20 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="B28" s="24">
+        <v>461</v>
+      </c>
+      <c r="B28" s="32">
         <f>IF(OR(COUNT('02_工况输入'!$C$72:$C$87)&lt;4,MOD(COUNT('02_工况输入'!$C$72:$C$87),4)&lt;&gt;0),"",AVERAGE(D5:D20))</f>
       </c>
       <c r="C28" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="28">
+      <c r="E28" s="36">
         <f>IF(OR(B27="",B28=""),"",B28/B27)</f>
       </c>
       <c r="F28" s="5" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -5185,7 +6929,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>463</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5194,7 +6938,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>367</v>
+        <v>464</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5203,187 +6947,187 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>465</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>358</v>
+        <v>455</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B5" s="21">
+        <v>467</v>
+      </c>
+      <c r="B5" s="29">
         <f>'03_管路水力'!B5</f>
         <v>8</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="27" t="str">
+      <c r="C5" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="35" t="str">
         <f>IF(B5="","待确认",IF(OR(B5="不适用",B5="待厂家确认",B5="待确认"),B5,"已计算"))</f>
         <v>已计算</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>371</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B6" s="22">
+        <v>469</v>
+      </c>
+      <c r="B6" s="30">
         <f>'03_管路水力'!B21</f>
         <v>0.6644468462342412</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="24" t="str">
+      <c r="C6" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="32" t="str">
         <f>IF(B6="","待确认",IF(OR(B6="不适用",B6="待厂家确认",B6="待确认"),B6,"已计算"))</f>
         <v>已计算</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>373</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B7" s="22">
+        <v>471</v>
+      </c>
+      <c r="B7" s="30">
         <f>'04_A路压力预算'!B10</f>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="24" t="str">
+      <c r="C7" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="32" t="str">
         <f>IF(B7="","待确认",IF(OR(B7="不适用",B7="待厂家确认",B7="待确认"),B7,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>375</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B8" s="22">
+        <v>473</v>
+      </c>
+      <c r="B8" s="30">
         <f>'04_A路压力预算'!C10</f>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="24" t="str">
+      <c r="C8" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="32" t="str">
         <f>IF(B8="","待确认",IF(OR(B8="不适用",B8="待厂家确认",B8="待确认"),B8,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>377</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B9" s="22">
+        <v>475</v>
+      </c>
+      <c r="B9" s="30">
         <f>IF('05_B路与文丘里'!B18&lt;&gt;"已计算","",'05_B路与文丘里'!B7)</f>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="24" t="str">
+      <c r="C9" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="32" t="str">
         <f>IF(B9="","待确认",IF(OR(B9="不适用",B9="待厂家确认",B9="待确认"),B9,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>379</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" s="22" t="str">
+        <v>429</v>
+      </c>
+      <c r="B10" s="30" t="str">
         <f>'05_B路与文丘里'!B18</f>
         <v>待厂家确认</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24" t="str">
+      <c r="C10" s="32"/>
+      <c r="D10" s="32" t="str">
         <f>IF(B10="","待确认",IF(OR(B10="不适用",B10="待厂家确认",B10="待确认"),B10,"已计算"))</f>
         <v>待厂家确认</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>380</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" s="22">
+        <v>446</v>
+      </c>
+      <c r="B11" s="30">
         <f>IF('06_肥液与桶'!B10="","",'06_肥液与桶'!B14)</f>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="24" t="str">
+      <c r="C11" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="32" t="str">
         <f>IF(B11="","待确认",IF(OR(B11="不适用",B11="待厂家确认",B11="待确认"),B11,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>381</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B12" s="22">
+        <v>458</v>
+      </c>
+      <c r="B12" s="30">
         <f>'07_冲洗与均匀度'!B26</f>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D12" s="24" t="str">
+      <c r="C12" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="32" t="str">
         <f>IF(B12="","待确认",IF(OR(B12="不适用",B12="待厂家确认",B12="待确认"),B12,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>382</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="B13" s="29">
+        <v>480</v>
+      </c>
+      <c r="B13" s="37">
         <f>IF(COUNT('02_工况输入'!$C$72:$C$87)&lt;4,"",'07_冲洗与均匀度'!E28)</f>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="D13" s="24" t="str">
+      <c r="C13" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="D13" s="32" t="str">
         <f>IF(B13="","待确认",IF(OR(B13="不适用",B13="待厂家确认",B13="待确认"),B13,"已计算"))</f>
         <v>待确认</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>384</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
-        <v>385</v>
+      <c r="A16" s="38" t="s">
+        <v>482</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -5392,10 +7136,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>386</v>
+        <v>483</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>387</v>
+        <v>484</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -5403,10 +7147,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>388</v>
+        <v>485</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>389</v>
+        <v>486</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
